--- a/experiments/results/resnet_imagenet50/ImageNet-1K/baseline/msp/adaptive/max/results.xlsx
+++ b/experiments/results/resnet_imagenet50/ImageNet-1K/baseline/msp/adaptive/max/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -577,6 +577,43 @@
       <c r="K6" s="4" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=6.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>58.92</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>65.70999999999999</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>82.53</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>91.67</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>51.62</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=10.0,type=max</t>
         </is>
       </c>
     </row>
